--- a/diseases/d031/2000-2004.xlsx
+++ b/diseases/d031/2000-2004.xlsx
@@ -5640,9 +5640,6 @@
       <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -6163,9 +6160,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6686,9 +6680,6 @@
       <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -7209,9 +7200,6 @@
       <c r="O37" t="n">
         <v>6</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -7732,9 +7720,6 @@
       <c r="O40" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -8255,9 +8240,6 @@
       <c r="O43" t="n">
         <v>7</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.0148798553712069</v>
       </c>
@@ -8778,9 +8760,6 @@
       <c r="O46" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -9301,9 +9280,6 @@
       <c r="O49" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -9824,9 +9800,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -10347,9 +10320,6 @@
       <c r="O55" t="n">
         <v>5</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.01062846812229064</v>
       </c>
@@ -10870,9 +10840,6 @@
       <c r="O58" t="n">
         <v>6</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -11393,9 +11360,6 @@
       <c r="O61" t="n">
         <v>6</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -11916,9 +11880,6 @@
       <c r="O64" t="n">
         <v>8</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -12439,9 +12400,6 @@
       <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -12962,9 +12920,6 @@
       <c r="O70" t="n">
         <v>5</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -13485,9 +13440,6 @@
       <c r="O73" t="n">
         <v>5</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -14008,9 +13960,6 @@
       <c r="O76" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -14531,9 +14480,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -15054,9 +15000,6 @@
       <c r="O82" t="n">
         <v>5</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -15577,9 +15520,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -16100,9 +16040,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -16623,9 +16560,6 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -17146,9 +17080,6 @@
       <c r="O94" t="n">
         <v>6</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.0126852252992738</v>
       </c>
@@ -17669,9 +17600,6 @@
       <c r="O97" t="n">
         <v>5</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -18192,9 +18120,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -18715,9 +18640,6 @@
       <c r="O103" t="n">
         <v>8</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.01683708586201371</v>
       </c>
@@ -19238,9 +19160,6 @@
       <c r="O106" t="n">
         <v>8</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.01683708586201371</v>
       </c>
@@ -19761,9 +19680,6 @@
       <c r="O109" t="n">
         <v>8</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.01683708586201371</v>
       </c>
@@ -20284,9 +20200,6 @@
       <c r="O112" t="n">
         <v>3</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -20807,9 +20720,6 @@
       <c r="O115" t="n">
         <v>13</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.02736026452577227</v>
       </c>
@@ -21330,9 +21240,6 @@
       <c r="O118" t="n">
         <v>9</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.01894172159476542</v>
       </c>
@@ -21853,9 +21760,6 @@
       <c r="O121" t="n">
         <v>4</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.008418542931006853</v>
       </c>
@@ -22376,9 +22280,6 @@
       <c r="O124" t="n">
         <v>7</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.01473245012926199</v>
       </c>
@@ -22899,9 +22800,6 @@
       <c r="O127" t="n">
         <v>10</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.02104635732751713</v>
       </c>
@@ -23422,9 +23320,6 @@
       <c r="O130" t="n">
         <v>24</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.05051125758604111</v>
       </c>
@@ -23945,9 +23840,6 @@
       <c r="O133" t="n">
         <v>12</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.02525562879302055</v>
       </c>
@@ -24468,9 +24360,6 @@
       <c r="O136" t="n">
         <v>8</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.01677251679717764</v>
       </c>
@@ -24991,9 +24880,6 @@
       <c r="O139" t="n">
         <v>4</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -25514,9 +25400,6 @@
       <c r="O142" t="n">
         <v>6</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -26037,9 +25920,6 @@
       <c r="O145" t="n">
         <v>5</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -26560,9 +26440,6 @@
       <c r="O148" t="n">
         <v>5</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -27083,9 +26960,6 @@
       <c r="O151" t="n">
         <v>6</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -27606,9 +27480,6 @@
       <c r="O154" t="n">
         <v>3</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -28129,9 +28000,6 @@
       <c r="O157" t="n">
         <v>3</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -28652,9 +28520,6 @@
       <c r="O160" t="n">
         <v>2</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -29175,9 +29040,6 @@
       <c r="O163" t="n">
         <v>11</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.02306221059611925</v>
       </c>
@@ -29698,9 +29560,6 @@
       <c r="O166" t="n">
         <v>16</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.03354503359435528</v>
       </c>
@@ -30220,9 +30079,6 @@
       </c>
       <c r="O169" t="n">
         <v>11</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0.02306221059611925</v>
